--- a/data/exercise_processing_log_carga.xlsx
+++ b/data/exercise_processing_log_carga.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlos.bermejo/Code/oupe-json-visualizer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BE6795-712B-224F-80EC-045324964BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542CF311-A44A-A645-89C1-FCA308B9C471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15460" xr2:uid="{FD7905CB-130A-4FEC-8BF1-F53B58F5998F}"/>
   </bookViews>
@@ -212,7 +212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -237,13 +237,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -681,14 +682,14 @@
     <col min="10" max="10" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" style="11"/>
+    <col min="13" max="13" width="11.5" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -697,10 +698,10 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -721,7 +722,7 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -754,7 +755,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="8"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="10"/>
+      <c r="M2" s="12"/>
       <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -787,7 +788,7 @@
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="9"/>
+      <c r="M3" s="11"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -819,7 +820,7 @@
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="9"/>
+      <c r="M4" s="11"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -851,7 +852,7 @@
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="9"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="9"/>
